--- a/marketing_report/outputs/Cursos/Matcheo_Completo/Solo_Matcheados_Cursos.xlsx
+++ b/marketing_report/outputs/Cursos/Matcheo_Completo/Solo_Matcheados_Cursos.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="396">
   <si>
     <t>Consulta: ID Consulta</t>
   </si>
@@ -349,21 +349,12 @@
     <t>003TV00000pMwMfYAK</t>
   </si>
   <si>
+    <t>003TV00000FLcM4YAL</t>
+  </si>
+  <si>
     <t>003TV0000059z31YAA</t>
   </si>
   <si>
-    <t>00QTV00000Vepl72AB</t>
-  </si>
-  <si>
-    <t>00QTV00000TdRUI2A3</t>
-  </si>
-  <si>
-    <t>00QTV00000RBIN42AP</t>
-  </si>
-  <si>
-    <t>00QTV00000RgMLC2A3</t>
-  </si>
-  <si>
     <t>003TV00000FLbznYAD</t>
   </si>
   <si>
@@ -376,30 +367,30 @@
     <t>00QTV0000027vq32AA</t>
   </si>
   <si>
-    <t>003TV00000FLcM4YAL</t>
+    <t>003TV000000w4o4YAA</t>
+  </si>
+  <si>
+    <t>00QTV00000CwCUv2AN</t>
+  </si>
+  <si>
+    <t>003TV00000CKRTPYA5</t>
+  </si>
+  <si>
+    <t>003TV00000blKdvYAE</t>
   </si>
   <si>
     <t>003TV000000r3rxYAA</t>
   </si>
   <si>
-    <t>003TV00000blKdvYAE</t>
-  </si>
-  <si>
     <t>003TV00000KhBG4YAN</t>
   </si>
   <si>
-    <t>00QTV00000CwCUv2AN</t>
-  </si>
-  <si>
-    <t>00QTV000000wF2D2AU</t>
-  </si>
-  <si>
-    <t>003TV00000CKRTPYA5</t>
-  </si>
-  <si>
     <t>rosavioletacala@gmail.com</t>
   </si>
   <si>
+    <t>fgimenez@ucasal.edu.ar</t>
+  </si>
+  <si>
     <t>carlasoledadgayo@gmail.com</t>
   </si>
   <si>
@@ -409,18 +400,6 @@
     <t>victoriadohrman@gmail.com</t>
   </si>
   <si>
-    <t>roxanaojeda_berisso@hotmail.com</t>
-  </si>
-  <si>
-    <t>giselagarrone03@gmail.com</t>
-  </si>
-  <si>
-    <t>verorescobar@hotmail.com</t>
-  </si>
-  <si>
-    <t>azullonghi@gmail.com</t>
-  </si>
-  <si>
     <t>antonellacarlamartinez2001@gmail.com</t>
   </si>
   <si>
@@ -433,36 +412,36 @@
     <t>veles.elisa18@gmail.com</t>
   </si>
   <si>
-    <t>fgimenez@ucasal.edu.ar</t>
+    <t>jazcabmont@gmail.com</t>
+  </si>
+  <si>
+    <t>xcardinali@gmail.com</t>
   </si>
   <si>
     <t>maraecortes@hotmail.com</t>
   </si>
   <si>
+    <t>friashugofranco@gmail.com</t>
+  </si>
+  <si>
+    <t>tolaban8@gmail.com</t>
+  </si>
+  <si>
+    <t>belensandovals29@gmail.com</t>
+  </si>
+  <si>
     <t>camilacavanna1@gmail.com</t>
   </si>
   <si>
-    <t>belensandovals29@gmail.com</t>
-  </si>
-  <si>
-    <t>jazcabmont@gmail.com</t>
-  </si>
-  <si>
     <t>tupacsebastiangarcia@gmail.com</t>
   </si>
   <si>
-    <t>friashugofranco@gmail.com</t>
-  </si>
-  <si>
-    <t>xcardinali@gmail.com</t>
-  </si>
-  <si>
-    <t>tolaban8@gmail.com</t>
-  </si>
-  <si>
     <t>jose</t>
   </si>
   <si>
+    <t>Francisco</t>
+  </si>
+  <si>
     <t>Carla Soledad Gayo</t>
   </si>
   <si>
@@ -472,18 +451,6 @@
     <t>Victoria</t>
   </si>
   <si>
-    <t>Roxana Ojeda</t>
-  </si>
-  <si>
-    <t>Gisela Garrone</t>
-  </si>
-  <si>
-    <t>Veronica Escobar</t>
-  </si>
-  <si>
-    <t>&amp;deg;Azul&amp;deg;</t>
-  </si>
-  <si>
     <t>Antonella Martinez</t>
   </si>
   <si>
@@ -496,78 +463,75 @@
     <t>Elisa Veles</t>
   </si>
   <si>
-    <t>Francisco</t>
+    <t>JAZMIN SALOME</t>
+  </si>
+  <si>
+    <t>XIMENA ROMINA</t>
   </si>
   <si>
     <t>Mara</t>
   </si>
   <si>
-    <t>Camila Jorgelina</t>
+    <t>Hugo Franco</t>
+  </si>
+  <si>
+    <t>Fernando</t>
   </si>
   <si>
     <t>ANA BELEN</t>
   </si>
   <si>
-    <t>JAZMIN SALOME</t>
+    <t>Camila</t>
   </si>
   <si>
     <t>Tupac</t>
   </si>
   <si>
-    <t>Hugo Franco</t>
-  </si>
-  <si>
-    <t>Ximena Romina Cardinali</t>
-  </si>
-  <si>
-    <t>Fernando</t>
-  </si>
-  <si>
     <t>10977449</t>
   </si>
   <si>
     <t>38850802</t>
   </si>
   <si>
+    <t>48781380</t>
+  </si>
+  <si>
+    <t>36130225</t>
+  </si>
+  <si>
     <t>34859579</t>
   </si>
   <si>
+    <t>37301681</t>
+  </si>
+  <si>
+    <t>44016484</t>
+  </si>
+  <si>
+    <t>47716777</t>
+  </si>
+  <si>
     <t>46323997</t>
   </si>
   <si>
-    <t>47716777</t>
-  </si>
-  <si>
-    <t>48781380</t>
-  </si>
-  <si>
     <t>44912612</t>
   </si>
   <si>
-    <t>37301681</t>
-  </si>
-  <si>
-    <t>36130225</t>
-  </si>
-  <si>
-    <t>44016484</t>
+    <t>Grado</t>
   </si>
   <si>
     <t>Pregrado</t>
   </si>
   <si>
-    <t>Grado</t>
-  </si>
-  <si>
-    <t>Educacion Continua</t>
-  </si>
-  <si>
     <t>Distancia</t>
   </si>
   <si>
     <t>Presencial</t>
   </si>
   <si>
+    <t>LICENCIATURA EN GASTRONOMÍA</t>
+  </si>
+  <si>
     <t>TECNICATURA UNIVERSITARIA EN GESTIÓN DE BANCOS, EMPRESAS FINANCIERAS Y DE SEG...</t>
   </si>
   <si>
@@ -577,15 +541,6 @@
     <t>ADMINISTRACIÓN DE EMPRESAS</t>
   </si>
   <si>
-    <t>TECNICATURA EN SEGURIDAD INFORMÁTICA</t>
-  </si>
-  <si>
-    <t>LICENCIATURA EN CRIMINOLOGÍA</t>
-  </si>
-  <si>
-    <t>INGRESO A LIC. EN TERAPIA OCUPACIONAL</t>
-  </si>
-  <si>
     <t>PROFESORADO EN  EDUCACIÓN FÍSICA</t>
   </si>
   <si>
@@ -598,96 +553,90 @@
     <t>ARQUITECTURA</t>
   </si>
   <si>
+    <t>CONTADOR PÚBLICO</t>
+  </si>
+  <si>
     <t>LICENCIATURA EN INGLÉS - CICLO DE LICENCIATURA</t>
   </si>
   <si>
+    <t>LICENCIATURA EN PRODUCCIÓN ANIMAL</t>
+  </si>
+  <si>
+    <t>CIENCIAS VETERINARIAS</t>
+  </si>
+  <si>
+    <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
+  </si>
+  <si>
     <t>GUÍA UNIVERSITARIO DE TURISMO</t>
   </si>
   <si>
-    <t>LICENCIATURA EN DISEÑO GRÁFICO</t>
-  </si>
-  <si>
-    <t>CONTADOR PÚBLICO</t>
-  </si>
-  <si>
     <t>LICENCIATURA EN COMERCIO INTERNACIONAL</t>
   </si>
   <si>
-    <t>LICENCIATURA EN PRODUCCIÓN ANIMAL</t>
-  </si>
-  <si>
-    <t>CIENCIAS VETERINARIAS</t>
+    <t>SALTA - CASTAÑARES PRESENCIAL</t>
   </si>
   <si>
     <t>SALTA - DISTANCIA Modo 7</t>
   </si>
   <si>
-    <t>SALTA - CASTAÑARES PRESENCIAL</t>
-  </si>
-  <si>
     <t>HOME</t>
   </si>
   <si>
-    <t>DELEGACION LA RIOJA - LA RIOJA</t>
+    <t>DELEGACION S S DE JUJUY - JUJUY</t>
+  </si>
+  <si>
+    <t>ig</t>
   </si>
   <si>
     <t>googleads</t>
   </si>
   <si>
-    <t>facebook</t>
+    <t>120235998797960048</t>
   </si>
   <si>
     <t>21676468921</t>
   </si>
   <si>
-    <t>carreras</t>
-  </si>
-  <si>
     <t>14876203835</t>
   </si>
   <si>
+    <t>paid</t>
+  </si>
+  <si>
     <t>leads</t>
   </si>
   <si>
-    <t>leadads</t>
-  </si>
-  <si>
-    <t>alcance</t>
-  </si>
-  <si>
-    <t>120237754753090048</t>
+    <t>120235998797950048</t>
   </si>
   <si>
     <t>ucasal</t>
   </si>
   <si>
-    <t>120215093246310048</t>
-  </si>
-  <si>
     <t>Contact_Center</t>
   </si>
   <si>
     <t>Contactados</t>
   </si>
   <si>
-    <t>No Contestan</t>
-  </si>
-  <si>
     <t>Abierto</t>
   </si>
   <si>
+    <t>Interesado</t>
+  </si>
+  <si>
     <t>No interesado</t>
   </si>
   <si>
-    <t>Interesado</t>
-  </si>
-  <si>
     <t>Solicitud creada</t>
   </si>
   <si>
     <t>27/2/2026</t>
   </si>
   <si>
+    <t>30/12/2025</t>
+  </si>
+  <si>
     <t>2025-11-26 00:00:00</t>
   </si>
   <si>
@@ -697,18 +646,6 @@
     <t>2025-09-01 00:00:00</t>
   </si>
   <si>
-    <t>26/2/2026</t>
-  </si>
-  <si>
-    <t>3/1/2026</t>
-  </si>
-  <si>
-    <t>2025-11-02 00:00:00</t>
-  </si>
-  <si>
-    <t>2025-11-12 00:00:00</t>
-  </si>
-  <si>
     <t>18/2/2026</t>
   </si>
   <si>
@@ -721,39 +658,30 @@
     <t>2025-11-22 00:00:00</t>
   </si>
   <si>
-    <t>30/12/2025</t>
+    <t>2025-09-02 00:00:00</t>
   </si>
   <si>
     <t>2025-09-29 00:00:00</t>
   </si>
   <si>
-    <t>2/7/2025</t>
+    <t>2025-01-19 00:00:00</t>
+  </si>
+  <si>
+    <t>27/1/2026</t>
   </si>
   <si>
     <t>27/8/2025</t>
   </si>
   <si>
-    <t>2025-09-02 00:00:00</t>
+    <t>4/8/2025</t>
   </si>
   <si>
     <t>2025-01-09 00:00:00</t>
   </si>
   <si>
-    <t>2025-01-19 00:00:00</t>
-  </si>
-  <si>
-    <t>2025-11-10 00:00:00</t>
-  </si>
-  <si>
-    <t>27/1/2026</t>
-  </si>
-  <si>
     <t>3.Frío</t>
   </si>
   <si>
-    <t>7/1/2026, 04:02</t>
-  </si>
-  <si>
     <t>19/2/2026, 14:02</t>
   </si>
   <si>
@@ -769,28 +697,25 @@
     <t>Victoria Dohrman</t>
   </si>
   <si>
-    <t>Veronica Escobar N/D</t>
-  </si>
-  <si>
-    <t>&amp;deg;Azul&amp;deg; N/D</t>
-  </si>
-  <si>
     <t>Belu&amp;lowbar;Davalos N/D</t>
   </si>
   <si>
     <t>Elisa Veles N/D</t>
   </si>
   <si>
+    <t>XIMENA ROMINA CARDINALI</t>
+  </si>
+  <si>
     <t>Mara Cortes</t>
   </si>
   <si>
+    <t>Hugo Franco Frias</t>
+  </si>
+  <si>
     <t>Tupac Garcia</t>
   </si>
   <si>
-    <t>Hugo Franco Frias</t>
-  </si>
-  <si>
-    <t>XIMENA ROMINA CARDINALI</t>
+    <t>Carolina Eugenia Ferrer</t>
   </si>
   <si>
     <t>Contact Center</t>
@@ -805,9 +730,6 @@
     <t>Jorge Ariel Cabaña</t>
   </si>
   <si>
-    <t>Carolina Eugenia Ferrer</t>
-  </si>
-  <si>
     <t>Rocío Belén Leiva</t>
   </si>
   <si>
@@ -817,27 +739,27 @@
     <t>SALTA - DISTANCIA</t>
   </si>
   <si>
-    <t>DELEGACION S S DE JUJUY - JUJUY</t>
-  </si>
-  <si>
     <t>CIENCIAS AGRARIAS Y VETERINARIAS</t>
   </si>
   <si>
+    <t>CENTRO DE IDIOMAS UCASAL</t>
+  </si>
+  <si>
     <t>FACULTAD DE EDUCACIÓN</t>
   </si>
   <si>
     <t>ARTES Y CIENCIAS</t>
   </si>
   <si>
-    <t>CENTRO DE IDIOMAS UCASAL</t>
-  </si>
-  <si>
     <t>FACULTAD DE CIENCIAS DE LA SALUD</t>
   </si>
   <si>
     <t>DIPLOMATURA UNIVERSITARIA EN TERAPIA NEURAL</t>
   </si>
   <si>
+    <t>CURSO REGULAR DE ITALIANO</t>
+  </si>
+  <si>
     <t>TALLER: PROGRAMA ESTRATÉGICO DE TITULACIÓN DE LA LICENCIATURA EN GESTIÓN EDUCATIVA</t>
   </si>
   <si>
@@ -847,33 +769,30 @@
     <t>CURSO REGULAR DE FRANCÉS</t>
   </si>
   <si>
+    <t>DIPLOMATURA EN REHABILITACIÓN Y READAPTACIÓN DEPORTIVA</t>
+  </si>
+  <si>
+    <t>DIPLOMATURA UNIVERSITARIA EN GAMIFICACIÓN Y NARRATIVA TRANSMEDIA. "TIZA Y PIXEL: INNOVANDO EN EL AULA DE LOS NIVELES PRIMARIO, SECUNDARIO Y SUPERIOR</t>
+  </si>
+  <si>
+    <t>CURSO REGULAR DE PORTUGUÉS</t>
+  </si>
+  <si>
     <t>CURSO INTENSIVO DE INGLÉS</t>
   </si>
   <si>
-    <t>DIPLOMATURA EN REHABILITACIÓN Y READAPTACIÓN DEPORTIVA</t>
-  </si>
-  <si>
-    <t>DIPLOMATURA UNIVERSITARIA EN GAMIFICACIÓN Y NARRATIVA TRANSMEDIA. "TIZA Y PIXEL: INNOVANDO EN EL AULA DE LOS NIVELES PRIMARIO, SECUNDARIO Y SUPERIOR</t>
-  </si>
-  <si>
-    <t>CURSO REGULAR DE PORTUGUÉS</t>
-  </si>
-  <si>
-    <t>CURSO REGULAR DE ITALIANO</t>
-  </si>
-  <si>
     <t>CURSO DE COREANO PRE A1</t>
   </si>
   <si>
+    <t>DIPLOMATURA UNIVERSITARIA EN ENFERMEDADES ZOONOTICAS EMERGENTES Y REEMERGENTES</t>
+  </si>
+  <si>
+    <t>DIPLOMATURA UNIVERSITARIA EN ANESTESIOLOGÍA Y ALGIOLOGÍA DE PEQUEÑOS ANIMALES</t>
+  </si>
+  <si>
     <t>CURSO DE JAPONÉS CON FINES ESPECÍFICOS</t>
   </si>
   <si>
-    <t>DIPLOMATURA UNIVERSITARIA EN ENFERMEDADES ZOONOTICAS EMERGENTES Y REEMERGENTES</t>
-  </si>
-  <si>
-    <t>DIPLOMATURA UNIVERSITARIA EN ANESTESIOLOGÍA Y ALGIOLOGÍA DE PEQUEÑOS ANIMALES</t>
-  </si>
-  <si>
     <t>CAMPUS VIRTUAL</t>
   </si>
   <si>
@@ -886,6 +805,9 @@
     <t>DNI-LE-LC</t>
   </si>
   <si>
+    <t>14222701</t>
+  </si>
+  <si>
     <t>29558435</t>
   </si>
   <si>
@@ -895,9 +817,6 @@
     <t>48338981</t>
   </si>
   <si>
-    <t>43218584</t>
-  </si>
-  <si>
     <t>43218927</t>
   </si>
   <si>
@@ -910,12 +829,12 @@
     <t>42917340</t>
   </si>
   <si>
-    <t>14222701</t>
-  </si>
-  <si>
     <t>CARLON , DANIEL</t>
   </si>
   <si>
+    <t>GIMÉNEZ ZAPIOLA, FRANCISCO</t>
+  </si>
+  <si>
     <t>GAYO, CARLA SOLEDAD</t>
   </si>
   <si>
@@ -925,9 +844,6 @@
     <t>DOHRMAN, VICTORIA</t>
   </si>
   <si>
-    <t>GIMENEZ LAGORIA , MARIA MICAELA</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARTINEZ , CARLA ANTONELLA </t>
   </si>
   <si>
@@ -940,36 +856,30 @@
     <t>VELES, ELISA MARIA FLORENCIA</t>
   </si>
   <si>
-    <t>GIMÉNEZ ZAPIOLA, FRANCISCO</t>
+    <t>CABRERIZO MONTERO, JAZMIN SALOME</t>
+  </si>
+  <si>
+    <t>CARDINALI, XIMENA ROMINA</t>
   </si>
   <si>
     <t>Cortes, Mara</t>
   </si>
   <si>
+    <t>Frias, Hugo Franco</t>
+  </si>
+  <si>
+    <t>TOLABA, FERNANDO NICOLAS</t>
+  </si>
+  <si>
+    <t>SANDOVALS, ANA BELEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAVANNA, CAMILA JORGELINA </t>
   </si>
   <si>
-    <t>SANDOVALS, ANA BELEN</t>
-  </si>
-  <si>
-    <t>CABRERIZO MONTERO, JAZMIN SALOME</t>
-  </si>
-  <si>
     <t>GARCIA, TUPAC SEBASTIAN</t>
   </si>
   <si>
-    <t>Frias, Hugo Franco</t>
-  </si>
-  <si>
-    <t>CARDINALI, XIMENA ROMINA</t>
-  </si>
-  <si>
-    <t>TOLABA, FERNANDO NICOLAS</t>
-  </si>
-  <si>
-    <t>marilagoria@gmail.com</t>
-  </si>
-  <si>
     <t>Martinezcarla981antonella@gmail.com</t>
   </si>
   <si>
@@ -985,24 +895,24 @@
     <t>yazmincabrerizo@gmail.com</t>
   </si>
   <si>
+    <t>ximena.rcardi@gmail.com</t>
+  </si>
+  <si>
     <t>tpgarciasebas@gmail.com</t>
   </si>
   <si>
-    <t>ximena.rcardi@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">- </t>
   </si>
   <si>
+    <t>387 - 5911005</t>
+  </si>
+  <si>
     <t>223 - 4879361</t>
   </si>
   <si>
     <t>387 - 4851679</t>
   </si>
   <si>
-    <t>0 - 0000</t>
-  </si>
-  <si>
     <t>387 - 5832169</t>
   </si>
   <si>
@@ -1015,24 +925,21 @@
     <t>387 - 4260918</t>
   </si>
   <si>
-    <t>387 - 5911005</t>
+    <t>387 - 4159718</t>
+  </si>
+  <si>
+    <t>387 - 4292954</t>
+  </si>
+  <si>
+    <t>387 - 4256349</t>
   </si>
   <si>
     <t>388 - 5087117</t>
   </si>
   <si>
-    <t>387 - 4159718</t>
-  </si>
-  <si>
     <t>387 - 5182052</t>
   </si>
   <si>
-    <t>387 - 4292954</t>
-  </si>
-  <si>
-    <t>387 - 4256349</t>
-  </si>
-  <si>
     <t>54 - 2235944297</t>
   </si>
   <si>
@@ -1042,39 +949,39 @@
     <t>-3874851679</t>
   </si>
   <si>
-    <t>387 - 4624817</t>
-  </si>
-  <si>
     <t>387 - 5016886</t>
   </si>
   <si>
     <t>387 - 2132387</t>
   </si>
   <si>
+    <t>387 - 6116543</t>
+  </si>
+  <si>
     <t>54 - 5493-875900111</t>
   </si>
   <si>
+    <t>54 - 5438-13007337</t>
+  </si>
+  <si>
+    <t>54 - 3874489311</t>
+  </si>
+  <si>
     <t>370 - 4520570</t>
   </si>
   <si>
-    <t>54 - 5438-13007337</t>
-  </si>
-  <si>
-    <t>387 - 6116543</t>
-  </si>
-  <si>
-    <t>54 - 3874489311</t>
+    <t>VENTAS - PRESENCIAL</t>
   </si>
   <si>
     <t>SUB SEDE JUJUY</t>
   </si>
   <si>
-    <t>VENTAS - PRESENCIAL</t>
-  </si>
-  <si>
     <t>VENTAS-DISTANCIA</t>
   </si>
   <si>
+    <t>ROMINA TAMARA PRADO</t>
+  </si>
+  <si>
     <t>CAMILA LAMAS CIL</t>
   </si>
   <si>
@@ -1090,27 +997,27 @@
     <t>MELINA SALVATIERRA</t>
   </si>
   <si>
-    <t>ROMINA TAMARA PRADO</t>
+    <t>GIMENA BEATRIZ VALLEJOS</t>
+  </si>
+  <si>
+    <t>KAREN IRIS MAMANI</t>
+  </si>
+  <si>
+    <t>PABLO SIMON SOTO</t>
   </si>
   <si>
     <t>ALEJO AGUSTIN BONARI</t>
   </si>
   <si>
-    <t>GIMENA BEATRIZ VALLEJOS</t>
-  </si>
-  <si>
     <t>DANIEL LUCIANO CHAILE SOTO</t>
   </si>
   <si>
-    <t>KAREN IRIS MAMANI</t>
-  </si>
-  <si>
-    <t>PABLO SIMON SOTO</t>
-  </si>
-  <si>
     <t>2026-02-11</t>
   </si>
   <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
     <t>2026-02-14</t>
   </si>
   <si>
@@ -1120,27 +1027,24 @@
     <t>2026-02-02</t>
   </si>
   <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2025-12-28</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
     <t>2026-02-04</t>
   </si>
   <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
     <t>2026-02-13</t>
   </si>
   <si>
@@ -1153,12 +1057,12 @@
     <t>2026-03-31</t>
   </si>
   <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
     <t>2026-03-01</t>
   </si>
   <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
     <t>9-2242175,18516380</t>
   </si>
   <si>
@@ -1171,9 +1075,6 @@
     <t>8-1957388,18436846</t>
   </si>
   <si>
-    <t>8-1961356,0</t>
-  </si>
-  <si>
     <t>9-2232767,18447451</t>
   </si>
   <si>
@@ -1183,27 +1084,30 @@
     <t>8-1958612,0</t>
   </si>
   <si>
+    <t>8-1967875,18492715</t>
+  </si>
+  <si>
     <t>9-2233844,18453706</t>
   </si>
   <si>
+    <t>9-2236524,18468250</t>
+  </si>
+  <si>
+    <t>8-1970181,18521353</t>
+  </si>
+  <si>
     <t>8-1963713,18467105</t>
   </si>
   <si>
-    <t>8-1967875,18492715</t>
-  </si>
-  <si>
     <t>8-1959175,18446158</t>
   </si>
   <si>
-    <t>9-2236524,18468250</t>
-  </si>
-  <si>
-    <t>8-1970181,18521353</t>
-  </si>
-  <si>
     <t>CARLON</t>
   </si>
   <si>
+    <t>GIMÉNEZ ZAPIOLA</t>
+  </si>
+  <si>
     <t>GAYO</t>
   </si>
   <si>
@@ -1213,9 +1117,6 @@
     <t>DOHRMAN</t>
   </si>
   <si>
-    <t>GIMENEZ LAGORIA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -1228,36 +1129,36 @@
     <t>VELES</t>
   </si>
   <si>
-    <t>GIMÉNEZ ZAPIOLA</t>
+    <t>CABRERIZO MONTERO</t>
+  </si>
+  <si>
+    <t>CARDINALI</t>
   </si>
   <si>
     <t>Cortes</t>
   </si>
   <si>
+    <t>Frias</t>
+  </si>
+  <si>
+    <t>TOLABA</t>
+  </si>
+  <si>
+    <t>SANDOVALS</t>
+  </si>
+  <si>
     <t>CAVANNA</t>
   </si>
   <si>
-    <t>SANDOVALS</t>
-  </si>
-  <si>
-    <t>CABRERIZO MONTERO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>Frias</t>
-  </si>
-  <si>
-    <t>CARDINALI</t>
-  </si>
-  <si>
-    <t>TOLABA</t>
-  </si>
-  <si>
     <t>DANIEL</t>
   </si>
   <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
     <t>CARLA SOLEDAD</t>
   </si>
   <si>
@@ -1267,9 +1168,6 @@
     <t>VICTORIA</t>
   </si>
   <si>
-    <t>MARIA MICAELA</t>
-  </si>
-  <si>
     <t>CARLA ANTONELLA</t>
   </si>
   <si>
@@ -1282,19 +1180,13 @@
     <t>ELISA MARIA FLORENCIA</t>
   </si>
   <si>
-    <t>FRANCISCO</t>
+    <t>FERNANDO NICOLAS</t>
   </si>
   <si>
     <t>CAMILA JORGELINA</t>
   </si>
   <si>
     <t>TUPAC SEBASTIAN</t>
-  </si>
-  <si>
-    <t>XIMENA ROMINA</t>
-  </si>
-  <si>
-    <t>FERNANDO NICOLAS</t>
   </si>
   <si>
     <t>Exacto (DNI)</t>
@@ -1676,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DE22"/>
+  <dimension ref="A1:DE18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -2122,103 +2014,103 @@
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F2">
         <v>54902266661904</v>
       </c>
       <c r="H2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="M2">
         <v>3</v>
       </c>
       <c r="S2" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="T2" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="U2" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="V2" t="s">
+        <v>204</v>
+      </c>
+      <c r="W2" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y2" t="s">
         <v>222</v>
       </c>
-      <c r="W2" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>246</v>
-      </c>
       <c r="AA2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="BB2">
         <v>148</v>
       </c>
       <c r="BC2" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="BD2">
         <v>9</v>
       </c>
       <c r="BE2" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="BF2">
         <v>1013</v>
       </c>
       <c r="BG2" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="BH2">
         <v>7</v>
       </c>
       <c r="BI2" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="BJ2" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK2" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="BM2" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="BN2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="BO2" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="BP2" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="BQ2">
         <v>11</v>
       </c>
       <c r="BV2" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="BW2">
         <v>75000</v>
       </c>
       <c r="BX2" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="BY2" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="BZ2">
         <v>2026</v>
@@ -2227,212 +2119,233 @@
         <v>50</v>
       </c>
       <c r="CB2" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="CC2" t="s">
+        <v>361</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>378</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>390</v>
+      </c>
+      <c r="DE2" t="s">
         <v>394</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>412</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>426</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:109">
       <c r="A3">
-        <v>1637433</v>
+        <v>1678082</v>
       </c>
       <c r="B3" t="s">
         <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F3">
-        <v>5492235944297</v>
+        <v>5493875911005</v>
       </c>
       <c r="G3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I3">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="J3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="M3">
-        <v>18</v>
-      </c>
-      <c r="S3" t="s">
-        <v>215</v>
+        <v>908</v>
+      </c>
+      <c r="N3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O3" t="s">
+        <v>191</v>
+      </c>
+      <c r="P3" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>196</v>
+      </c>
+      <c r="R3">
+        <v>1.2023729650832E+17</v>
+      </c>
+      <c r="T3" t="s">
+        <v>199</v>
       </c>
       <c r="U3" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="V3" t="s">
-        <v>223</v>
+        <v>205</v>
+      </c>
+      <c r="W3" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>140</v>
       </c>
       <c r="AC3" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="BB3">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>185</v>
+      </c>
+      <c r="BD3">
+        <v>24</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>241</v>
+      </c>
+      <c r="BF3">
+        <v>964</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>246</v>
+      </c>
+      <c r="BH3">
+        <v>1</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>259</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>261</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>262</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>271</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>123</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>295</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>295</v>
+      </c>
+      <c r="BQ3">
+        <v>1</v>
+      </c>
+      <c r="BR3">
         <v>3</v>
       </c>
-      <c r="BC3" t="s">
-        <v>265</v>
-      </c>
-      <c r="BD3">
-        <v>21</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>268</v>
-      </c>
-      <c r="BF3">
-        <v>1225</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>273</v>
-      </c>
-      <c r="BH3">
-        <v>7</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>285</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>289</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>299</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>127</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>325</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>338</v>
-      </c>
-      <c r="BQ3">
-        <v>11</v>
-      </c>
-      <c r="BR3">
-        <v>101</v>
-      </c>
       <c r="BS3" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="BT3">
-        <v>1010</v>
+        <v>1731</v>
       </c>
       <c r="BU3" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="BV3" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="BW3">
-        <v>45000</v>
+        <v>56500</v>
       </c>
       <c r="BX3" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY3" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="BZ3">
         <v>2026</v>
       </c>
-      <c r="CA3">
-        <v>50</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>381</v>
-      </c>
       <c r="CC3" t="s">
+        <v>362</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>379</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>391</v>
+      </c>
+      <c r="DE3" t="s">
         <v>395</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>413</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>427</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:109">
       <c r="A4">
-        <v>1600059</v>
+        <v>1637433</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F4">
-        <v>5493874524097</v>
+        <v>5492235944297</v>
       </c>
       <c r="G4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="H4" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="I4">
-        <v>383</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="K4">
         <v>3</v>
       </c>
       <c r="L4" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="M4">
         <v>18</v>
       </c>
       <c r="S4" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="U4" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="V4" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="AC4" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -2441,73 +2354,73 @@
         <v>3</v>
       </c>
       <c r="BC4" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="BD4">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="BF4">
-        <v>1681</v>
+        <v>1225</v>
       </c>
       <c r="BG4" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="BH4">
         <v>7</v>
       </c>
       <c r="BI4" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="BJ4" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK4" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL4" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="BM4" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="BN4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="BO4" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="BP4" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="BQ4">
         <v>11</v>
       </c>
       <c r="BR4">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="BS4" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="BT4">
-        <v>1750</v>
+        <v>1010</v>
       </c>
       <c r="BU4" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="BV4" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="BW4">
-        <v>50000</v>
+        <v>45000</v>
       </c>
       <c r="BX4" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY4" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ4">
         <v>2026</v>
@@ -2516,141 +2429,141 @@
         <v>50</v>
       </c>
       <c r="CB4" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="CC4" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="CD4" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="CE4" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="DE4" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:109">
       <c r="A5">
-        <v>1523940</v>
+        <v>1600059</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F5">
-        <v>543874851679</v>
+        <v>5493874524097</v>
       </c>
       <c r="G5" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="H5" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>383</v>
       </c>
       <c r="J5" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="S5" t="s">
+        <v>198</v>
       </c>
       <c r="U5" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="V5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="AC5" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>239</v>
+      </c>
+      <c r="BD5">
         <v>1</v>
       </c>
-      <c r="BC5" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD5">
-        <v>24</v>
-      </c>
       <c r="BE5" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="BF5">
-        <v>963</v>
+        <v>1681</v>
       </c>
       <c r="BG5" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="BH5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BI5" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="BJ5" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK5" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL5" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="BM5" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="BN5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="BO5" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="BP5" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="BQ5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BR5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS5" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="BT5">
-        <v>1334</v>
+        <v>1750</v>
       </c>
       <c r="BU5" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="BV5" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="BW5">
-        <v>113000</v>
+        <v>50000</v>
       </c>
       <c r="BX5" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY5" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ5">
         <v>2026</v>
@@ -2659,84 +2572,66 @@
         <v>50</v>
       </c>
       <c r="CB5" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="CC5" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="CD5" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="CE5" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="DE5" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:109">
       <c r="A6">
-        <v>1789735</v>
-      </c>
-      <c r="B6" t="s">
-        <v>111</v>
+        <v>1523940</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>543874851679</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I6">
-        <v>360</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="M6">
-        <v>18</v>
-      </c>
-      <c r="S6" t="s">
-        <v>215</v>
-      </c>
-      <c r="T6" t="s">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="U6" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="V6" t="s">
-        <v>226</v>
-      </c>
-      <c r="W6" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="AA6" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AC6" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -2745,61 +2640,73 @@
         <v>1</v>
       </c>
       <c r="BC6" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BD6">
         <v>24</v>
       </c>
       <c r="BE6" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="BF6">
-        <v>1050</v>
+        <v>963</v>
       </c>
       <c r="BG6" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="BH6">
         <v>1</v>
       </c>
       <c r="BI6" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="BJ6" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK6" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL6" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="BM6" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="BN6" t="s">
-        <v>316</v>
+        <v>126</v>
       </c>
       <c r="BO6" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="BP6" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="BQ6">
         <v>1</v>
       </c>
+      <c r="BR6">
+        <v>2</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>319</v>
+      </c>
+      <c r="BT6">
+        <v>1334</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>323</v>
+      </c>
       <c r="BV6" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="BW6">
-        <v>56500</v>
+        <v>113000</v>
       </c>
       <c r="BX6" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="BY6" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="BZ6">
         <v>2026</v>
@@ -2808,150 +2715,162 @@
         <v>50</v>
       </c>
       <c r="CB6" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="CC6" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="CD6" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="CE6" t="s">
-        <v>428</v>
+        <v>391</v>
       </c>
       <c r="DE6" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:109">
       <c r="A7">
-        <v>1682222</v>
+        <v>1773800</v>
       </c>
       <c r="B7" t="s">
         <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F7">
-        <v>5490000</v>
+        <v>543875832169</v>
       </c>
       <c r="G7" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I7">
-        <v>393</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="s">
+        <v>185</v>
+      </c>
+      <c r="M7">
+        <v>907</v>
+      </c>
+      <c r="S7" t="s">
+        <v>198</v>
+      </c>
+      <c r="T7" t="s">
+        <v>199</v>
+      </c>
+      <c r="U7" t="s">
         <v>200</v>
       </c>
-      <c r="M7">
-        <v>18</v>
-      </c>
-      <c r="S7" t="s">
-        <v>215</v>
-      </c>
-      <c r="T7" t="s">
-        <v>217</v>
-      </c>
-      <c r="U7" t="s">
-        <v>218</v>
-      </c>
       <c r="V7" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="W7" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="X7" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="Y7" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="AA7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AB7" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AC7" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="AD7">
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC7" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="BD7">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BE7" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="BF7">
-        <v>1050</v>
+        <v>1588</v>
       </c>
       <c r="BG7" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="BH7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BI7" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="BJ7" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>261</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>266</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>275</v>
+      </c>
+      <c r="BN7" t="s">
         <v>287</v>
       </c>
-      <c r="BK7" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>292</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>302</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>316</v>
-      </c>
       <c r="BO7" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="BP7" t="s">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="BQ7">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="BR7">
+        <v>3</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>317</v>
+      </c>
+      <c r="BT7">
+        <v>2191</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>324</v>
       </c>
       <c r="BV7" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="BW7">
-        <v>56500</v>
+        <v>130000</v>
       </c>
       <c r="BX7" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="BY7" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="BZ7">
         <v>2026</v>
@@ -2960,138 +2879,150 @@
         <v>50</v>
       </c>
       <c r="CB7" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="CC7" t="s">
-        <v>398</v>
+        <v>366</v>
       </c>
       <c r="CD7" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="CE7" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="DE7" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:109">
       <c r="A8">
-        <v>1607267</v>
+        <v>1722167</v>
       </c>
       <c r="B8" t="s">
         <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>145</v>
+      </c>
+      <c r="E8" t="s">
+        <v>157</v>
       </c>
       <c r="F8">
-        <v>5490000</v>
+        <v>5493885080215</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I8">
-        <v>1201</v>
+        <v>113</v>
       </c>
       <c r="J8" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="L8" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="M8">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S8" t="s">
-        <v>215</v>
+        <v>198</v>
+      </c>
+      <c r="T8" t="s">
+        <v>199</v>
       </c>
       <c r="U8" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="V8" t="s">
-        <v>228</v>
+        <v>210</v>
+      </c>
+      <c r="W8" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>222</v>
       </c>
       <c r="AA8" t="s">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="AB8" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AC8" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="AD8">
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="BD8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE8" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="BF8">
-        <v>1050</v>
+        <v>1583</v>
       </c>
       <c r="BG8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BH8">
+        <v>7</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>258</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>261</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>267</v>
+      </c>
+      <c r="BM8" t="s">
         <v>276</v>
       </c>
-      <c r="BH8">
-        <v>1</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>286</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK8" t="s">
+      <c r="BN8" t="s">
         <v>288</v>
       </c>
-      <c r="BL8" t="s">
-        <v>292</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>302</v>
-      </c>
-      <c r="BN8" t="s">
-        <v>316</v>
-      </c>
       <c r="BO8" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="BP8" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="BQ8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BV8" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="BW8">
-        <v>56500</v>
+        <v>75000</v>
       </c>
       <c r="BX8" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="BY8" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="BZ8">
         <v>2026</v>
@@ -3100,75 +3031,78 @@
         <v>50</v>
       </c>
       <c r="CB8" t="s">
+        <v>353</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>367</v>
+      </c>
+      <c r="CD8" t="s">
         <v>384</v>
       </c>
-      <c r="CC8" t="s">
-        <v>398</v>
-      </c>
-      <c r="CD8" t="s">
-        <v>416</v>
-      </c>
       <c r="CE8" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="DE8" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:109">
       <c r="A9">
-        <v>1617917</v>
+        <v>1655372</v>
       </c>
       <c r="B9" t="s">
         <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F9">
-        <v>5490000</v>
+        <v>543875016886</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I9">
-        <v>393</v>
+        <v>187</v>
       </c>
       <c r="J9" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="M9">
-        <v>18</v>
-      </c>
-      <c r="S9" t="s">
-        <v>215</v>
+        <v>4</v>
+      </c>
+      <c r="N9" t="s">
+        <v>190</v>
+      </c>
+      <c r="O9" t="s">
+        <v>192</v>
+      </c>
+      <c r="P9" t="s">
+        <v>195</v>
       </c>
       <c r="U9" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="V9" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AA9" t="s">
-        <v>251</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="AC9" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -3177,61 +3111,73 @@
         <v>1</v>
       </c>
       <c r="BC9" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BD9">
         <v>24</v>
       </c>
       <c r="BE9" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="BF9">
-        <v>1050</v>
+        <v>965</v>
       </c>
       <c r="BG9" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="BH9">
         <v>1</v>
       </c>
       <c r="BI9" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="BJ9" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK9" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL9" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="BM9" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="BN9" t="s">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="BO9" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="BP9" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="BQ9">
         <v>1</v>
       </c>
+      <c r="BR9">
+        <v>3</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>317</v>
+      </c>
+      <c r="BT9">
+        <v>1872</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>325</v>
+      </c>
       <c r="BV9" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="BW9">
         <v>56500</v>
       </c>
       <c r="BX9" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="BY9" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
       <c r="BZ9">
         <v>2026</v>
@@ -3240,314 +3186,281 @@
         <v>50</v>
       </c>
       <c r="CB9" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="CC9" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="CD9" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="CE9" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="DE9" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:109">
       <c r="A10">
-        <v>1773800</v>
+        <v>1632747</v>
       </c>
       <c r="B10" t="s">
         <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F10">
-        <v>543875832169</v>
+        <v>543872132387</v>
       </c>
       <c r="G10" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I10">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
+        <v>185</v>
+      </c>
+      <c r="M10">
+        <v>272</v>
+      </c>
+      <c r="U10" t="s">
         <v>201</v>
       </c>
-      <c r="M10">
-        <v>907</v>
-      </c>
-      <c r="S10" t="s">
-        <v>215</v>
-      </c>
-      <c r="T10" t="s">
-        <v>216</v>
-      </c>
-      <c r="U10" t="s">
-        <v>218</v>
-      </c>
       <c r="V10" t="s">
-        <v>230</v>
-      </c>
-      <c r="W10" t="s">
-        <v>243</v>
-      </c>
-      <c r="X10" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="AA10" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="AB10" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AC10" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="AD10">
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC10" t="s">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="BD10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="BF10">
-        <v>1588</v>
+        <v>1050</v>
       </c>
       <c r="BG10" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="BH10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BI10" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="BJ10" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK10" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL10" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="BM10" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="BN10" t="s">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="BO10" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="BP10" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="BQ10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BR10">
         <v>3</v>
       </c>
       <c r="BS10" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="BT10">
-        <v>2191</v>
+        <v>1750</v>
       </c>
       <c r="BU10" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="BV10" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="BW10">
-        <v>130000</v>
+        <v>56500</v>
       </c>
       <c r="BX10" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY10" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ10">
         <v>2026</v>
       </c>
-      <c r="CA10">
-        <v>50</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>385</v>
-      </c>
       <c r="CC10" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="CD10" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="CE10" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="DE10" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:109">
       <c r="A11">
-        <v>1722167</v>
-      </c>
-      <c r="B11" t="s">
-        <v>116</v>
+        <v>1525685</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11">
+        <v>3874159718</v>
+      </c>
+      <c r="G11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" t="s">
         <v>169</v>
       </c>
-      <c r="F11">
-        <v>5493885080215</v>
-      </c>
-      <c r="G11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H11" t="s">
-        <v>181</v>
-      </c>
       <c r="I11">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="K11">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>202</v>
-      </c>
-      <c r="M11">
+        <v>185</v>
+      </c>
+      <c r="U11" t="s">
+        <v>203</v>
+      </c>
+      <c r="V11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="BB11">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>185</v>
+      </c>
+      <c r="BD11">
+        <v>24</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>241</v>
+      </c>
+      <c r="BF11">
+        <v>1157</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>254</v>
+      </c>
+      <c r="BH11">
+        <v>1</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>259</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>261</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>158</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>279</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>291</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>302</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>302</v>
+      </c>
+      <c r="BQ11">
+        <v>1</v>
+      </c>
+      <c r="BR11">
         <v>3</v>
       </c>
-      <c r="S11" t="s">
-        <v>215</v>
-      </c>
-      <c r="T11" t="s">
-        <v>216</v>
-      </c>
-      <c r="U11" t="s">
-        <v>219</v>
-      </c>
-      <c r="V11" t="s">
-        <v>231</v>
-      </c>
-      <c r="W11" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>246</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>10</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>266</v>
-      </c>
-      <c r="BD11">
-        <v>21</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BF11">
-        <v>1583</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>278</v>
-      </c>
-      <c r="BH11">
-        <v>7</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>285</v>
-      </c>
-      <c r="BJ11" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>294</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>304</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>318</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>329</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>329</v>
-      </c>
-      <c r="BQ11">
-        <v>11</v>
+      <c r="BS11" t="s">
+        <v>317</v>
+      </c>
+      <c r="BT11">
+        <v>1731</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>320</v>
       </c>
       <c r="BV11" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="BW11">
-        <v>75000</v>
+        <v>90300</v>
       </c>
       <c r="BX11" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="BY11" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ11">
         <v>2026</v>
@@ -3556,78 +3469,72 @@
         <v>50</v>
       </c>
       <c r="CB11" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="CC11" t="s">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="CD11" t="s">
-        <v>418</v>
+        <v>148</v>
       </c>
       <c r="CE11" t="s">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="DE11" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:109">
       <c r="A12">
-        <v>1655372</v>
+        <v>1637467</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>149</v>
+      </c>
+      <c r="E12" t="s">
+        <v>159</v>
       </c>
       <c r="F12">
-        <v>543875016886</v>
+        <v>5493876116543</v>
       </c>
       <c r="G12" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H12" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I12">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M12">
-        <v>4</v>
-      </c>
-      <c r="N12" t="s">
-        <v>204</v>
-      </c>
-      <c r="O12" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" t="s">
+        <v>202</v>
+      </c>
+      <c r="V12" t="s">
         <v>206</v>
       </c>
-      <c r="P12" t="s">
-        <v>209</v>
-      </c>
-      <c r="U12" t="s">
-        <v>220</v>
-      </c>
-      <c r="V12" t="s">
-        <v>232</v>
-      </c>
       <c r="AA12" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="AC12" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -3636,46 +3543,46 @@
         <v>1</v>
       </c>
       <c r="BC12" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BD12">
         <v>24</v>
       </c>
       <c r="BE12" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="BF12">
-        <v>965</v>
+        <v>1050</v>
       </c>
       <c r="BG12" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="BH12">
         <v>1</v>
       </c>
       <c r="BI12" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="BJ12" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK12" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL12" t="s">
-        <v>295</v>
+        <v>159</v>
       </c>
       <c r="BM12" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="BN12" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="BO12" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="BP12" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="BQ12">
         <v>1</v>
@@ -3684,481 +3591,481 @@
         <v>3</v>
       </c>
       <c r="BS12" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="BT12">
-        <v>1872</v>
+        <v>10</v>
       </c>
       <c r="BU12" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="BV12" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="BW12">
         <v>56500</v>
       </c>
       <c r="BX12" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY12" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="BZ12">
         <v>2026</v>
       </c>
-      <c r="CA12">
-        <v>50</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>387</v>
-      </c>
       <c r="CC12" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="CD12" t="s">
-        <v>419</v>
+        <v>149</v>
       </c>
       <c r="CE12" t="s">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="DE12" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:109">
       <c r="A13">
-        <v>1632747</v>
-      </c>
-      <c r="B13" t="s">
-        <v>118</v>
+        <v>1560194</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="E13" t="s">
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>543872132387</v>
+        <v>543875900111</v>
       </c>
       <c r="G13" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I13">
+        <v>94</v>
+      </c>
+      <c r="J13" t="s">
         <v>179</v>
-      </c>
-      <c r="H13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I13">
-        <v>26</v>
-      </c>
-      <c r="J13" t="s">
-        <v>192</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="M13">
-        <v>272</v>
+        <v>18</v>
+      </c>
+      <c r="S13" t="s">
+        <v>198</v>
       </c>
       <c r="U13" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="V13" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>229</v>
+      </c>
+      <c r="AC13" t="s">
         <v>233</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>261</v>
       </c>
       <c r="AD13">
         <v>0</v>
       </c>
       <c r="BB13">
+        <v>3</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>239</v>
+      </c>
+      <c r="BD13">
         <v>1</v>
       </c>
-      <c r="BC13" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD13">
-        <v>24</v>
-      </c>
       <c r="BE13" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="BF13">
-        <v>1050</v>
+        <v>1681</v>
       </c>
       <c r="BG13" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="BH13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BI13" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="BJ13" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK13" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL13" t="s">
-        <v>296</v>
+        <v>160</v>
       </c>
       <c r="BM13" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="BN13" t="s">
-        <v>320</v>
+        <v>133</v>
       </c>
       <c r="BO13" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="BP13" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="BQ13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BR13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS13" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="BT13">
-        <v>1750</v>
+        <v>1334</v>
       </c>
       <c r="BU13" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="BV13" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="BW13">
-        <v>56500</v>
+        <v>50000</v>
       </c>
       <c r="BX13" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY13" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ13">
         <v>2026</v>
       </c>
+      <c r="CA13">
+        <v>50</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>356</v>
+      </c>
       <c r="CC13" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="CD13" t="s">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="CE13" t="s">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="DE13" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:109">
       <c r="A14">
-        <v>1678073</v>
+        <v>1249246</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="E14" t="s">
+        <v>161</v>
       </c>
       <c r="F14">
-        <v>5493875911005</v>
+        <v>543813007337</v>
       </c>
       <c r="G14" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H14" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I14">
-        <v>360</v>
+        <v>231</v>
       </c>
       <c r="J14" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="M14">
-        <v>443</v>
-      </c>
-      <c r="N14" t="s">
-        <v>205</v>
-      </c>
-      <c r="O14" t="s">
-        <v>207</v>
-      </c>
-      <c r="P14" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>212</v>
-      </c>
-      <c r="R14">
-        <v>1.2023893598175E+17</v>
-      </c>
-      <c r="T14" t="s">
-        <v>216</v>
+        <v>18</v>
+      </c>
+      <c r="S14" t="s">
+        <v>198</v>
       </c>
       <c r="U14" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="V14" t="s">
-        <v>234</v>
-      </c>
-      <c r="W14" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="AA14" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="AC14" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="AD14">
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="BD14">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BE14" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="BF14">
-        <v>964</v>
+        <v>1512</v>
       </c>
       <c r="BG14" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="BH14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BI14" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="BJ14" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK14" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL14" t="s">
-        <v>297</v>
+        <v>161</v>
       </c>
       <c r="BM14" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="BN14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BO14" t="s">
-        <v>332</v>
+        <v>294</v>
       </c>
       <c r="BP14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="BQ14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BR14">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="BS14" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="BT14">
-        <v>1731</v>
+        <v>2251</v>
       </c>
       <c r="BU14" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="BV14" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="BW14">
-        <v>56500</v>
+        <v>60000</v>
       </c>
       <c r="BX14" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY14" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="BZ14">
         <v>2026</v>
       </c>
+      <c r="CA14">
+        <v>50</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>357</v>
+      </c>
       <c r="CC14" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="CD14" t="s">
-        <v>421</v>
+        <v>151</v>
       </c>
       <c r="CE14" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="DE14" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:109">
       <c r="A15">
-        <v>1560194</v>
+        <v>1727395</v>
+      </c>
+      <c r="B15" t="s">
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F15">
-        <v>543875900111</v>
+        <v>5493874489311</v>
       </c>
       <c r="G15" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H15" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I15">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="J15" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="M15">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S15" t="s">
-        <v>215</v>
+        <v>198</v>
+      </c>
+      <c r="T15" t="s">
+        <v>199</v>
       </c>
       <c r="U15" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="V15" t="s">
-        <v>235</v>
+        <v>216</v>
+      </c>
+      <c r="W15" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>222</v>
       </c>
       <c r="AA15" t="s">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="AC15" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="AD15">
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC15" t="s">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="BD15">
+        <v>9</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>240</v>
+      </c>
+      <c r="BF15">
+        <v>1644</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>256</v>
+      </c>
+      <c r="BH15">
         <v>1</v>
       </c>
-      <c r="BE15" t="s">
-        <v>269</v>
-      </c>
-      <c r="BF15">
-        <v>1681</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>274</v>
-      </c>
-      <c r="BH15">
-        <v>7</v>
-      </c>
       <c r="BI15" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="BJ15" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK15" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="BM15" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="BN15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BO15" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="BP15" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="BQ15">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BR15">
         <v>2</v>
       </c>
       <c r="BS15" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="BT15">
-        <v>1334</v>
+        <v>2491</v>
       </c>
       <c r="BU15" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="BV15" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="BW15">
-        <v>50000</v>
+        <v>175000</v>
       </c>
       <c r="BX15" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY15" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ15">
         <v>2026</v>
@@ -4167,123 +4074,123 @@
         <v>50</v>
       </c>
       <c r="CB15" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="CC15" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="CD15" t="s">
-        <v>160</v>
+        <v>387</v>
       </c>
       <c r="CE15" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="DE15" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:109">
       <c r="A16">
-        <v>1471982</v>
+        <v>1520798</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F16">
-        <v>5493885087117</v>
+        <v>3704520570</v>
       </c>
       <c r="G16" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H16" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="I16">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="J16" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K16">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L16" t="s">
+        <v>185</v>
+      </c>
+      <c r="T16" t="s">
+        <v>199</v>
+      </c>
+      <c r="U16" t="s">
         <v>203</v>
       </c>
-      <c r="M16">
-        <v>3</v>
-      </c>
-      <c r="T16" t="s">
-        <v>216</v>
-      </c>
-      <c r="U16" t="s">
-        <v>219</v>
-      </c>
       <c r="V16" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="W16" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="Y16" t="s">
-        <v>246</v>
+        <v>223</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>224</v>
       </c>
       <c r="AA16" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="BB16">
         <v>1</v>
       </c>
       <c r="BC16" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BD16">
         <v>24</v>
       </c>
       <c r="BE16" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="BF16">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="BG16" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="BH16">
         <v>1</v>
       </c>
       <c r="BI16" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="BJ16" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK16" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL16" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="BM16" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="BN16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BO16" t="s">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="BP16" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="BQ16">
         <v>1</v>
@@ -4292,144 +4199,150 @@
         <v>3</v>
       </c>
       <c r="BS16" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="BT16">
-        <v>1110</v>
+        <v>10</v>
       </c>
       <c r="BU16" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="BV16" t="s">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="BW16">
-        <v>56500</v>
+        <v>90300</v>
       </c>
       <c r="BX16" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY16" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ16">
         <v>2026</v>
       </c>
+      <c r="CA16">
+        <v>50</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>359</v>
+      </c>
       <c r="CC16" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="CD16" t="s">
-        <v>422</v>
+        <v>153</v>
       </c>
       <c r="CE16" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="DE16" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:109">
       <c r="A17">
-        <v>1520798</v>
+        <v>1506586</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E17" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F17">
-        <v>3704520570</v>
+        <v>54903885087117</v>
       </c>
       <c r="G17" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="H17" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I17">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="s">
-        <v>201</v>
+        <v>188</v>
+      </c>
+      <c r="M17">
+        <v>3</v>
       </c>
       <c r="T17" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="U17" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="V17" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="W17" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="Y17" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="AA17" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="BB17">
         <v>1</v>
       </c>
       <c r="BC17" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BD17">
         <v>24</v>
       </c>
       <c r="BE17" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="BF17">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="BG17" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="BH17">
         <v>1</v>
       </c>
       <c r="BI17" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="BJ17" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="BK17" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="BL17" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="BM17" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="BN17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="BO17" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="BP17" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="BQ17">
         <v>1</v>
@@ -4438,138 +4351,156 @@
         <v>3</v>
       </c>
       <c r="BS17" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="BT17">
-        <v>10</v>
+        <v>1110</v>
       </c>
       <c r="BU17" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="BV17" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="BW17">
-        <v>90300</v>
+        <v>56500</v>
       </c>
       <c r="BX17" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY17" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ17">
         <v>2026</v>
       </c>
-      <c r="CA17">
-        <v>50</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>389</v>
-      </c>
       <c r="CC17" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="CD17" t="s">
-        <v>162</v>
+        <v>388</v>
       </c>
       <c r="CE17" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="DE17" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:109">
       <c r="A18">
-        <v>1525685</v>
+        <v>1236872</v>
+      </c>
+      <c r="B18" t="s">
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F18">
-        <v>3874159718</v>
+        <v>543875182052</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="H18" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I18">
-        <v>14</v>
+        <v>214</v>
       </c>
       <c r="J18" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>201</v>
+        <v>185</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18" t="s">
+        <v>190</v>
+      </c>
+      <c r="O18" t="s">
+        <v>193</v>
+      </c>
+      <c r="P18" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>197</v>
+      </c>
+      <c r="R18">
+        <v>619288243159</v>
       </c>
       <c r="U18" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="V18" t="s">
-        <v>238</v>
+        <v>219</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>231</v>
       </c>
       <c r="AC18" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="AD18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB18">
         <v>1</v>
       </c>
       <c r="BC18" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="BD18">
         <v>24</v>
       </c>
       <c r="BE18" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="BF18">
-        <v>1157</v>
+        <v>1594</v>
       </c>
       <c r="BG18" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="BH18">
         <v>1</v>
       </c>
       <c r="BI18" t="s">
+        <v>259</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>261</v>
+      </c>
+      <c r="BL18" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM18" t="s">
         <v>286</v>
       </c>
-      <c r="BJ18" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK18" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL18" t="s">
-        <v>173</v>
-      </c>
-      <c r="BM18" t="s">
-        <v>311</v>
-      </c>
       <c r="BN18" t="s">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="BO18" t="s">
-        <v>334</v>
+        <v>306</v>
       </c>
       <c r="BP18" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="BQ18">
         <v>1</v>
@@ -4578,25 +4509,25 @@
         <v>3</v>
       </c>
       <c r="BS18" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="BT18">
-        <v>1731</v>
+        <v>2190</v>
       </c>
       <c r="BU18" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="BV18" t="s">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="BW18">
         <v>90300</v>
       </c>
       <c r="BX18" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="BY18" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="BZ18">
         <v>2026</v>
@@ -4605,657 +4536,19 @@
         <v>50</v>
       </c>
       <c r="CB18" t="s">
+        <v>360</v>
+      </c>
+      <c r="CC18" t="s">
+        <v>377</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>389</v>
+      </c>
+      <c r="CE18" t="s">
         <v>390</v>
       </c>
-      <c r="CC18" t="s">
-        <v>407</v>
-      </c>
-      <c r="CD18" t="s">
-        <v>163</v>
-      </c>
-      <c r="CE18" t="s">
-        <v>426</v>
-      </c>
       <c r="DE18" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="19" spans="1:109">
-      <c r="A19">
-        <v>1236872</v>
-      </c>
-      <c r="B19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" t="s">
-        <v>164</v>
-      </c>
-      <c r="E19" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19">
-        <v>543875182052</v>
-      </c>
-      <c r="G19" t="s">
-        <v>179</v>
-      </c>
-      <c r="H19" t="s">
-        <v>182</v>
-      </c>
-      <c r="I19">
-        <v>214</v>
-      </c>
-      <c r="J19" t="s">
-        <v>197</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>201</v>
-      </c>
-      <c r="M19">
-        <v>4</v>
-      </c>
-      <c r="N19" t="s">
-        <v>204</v>
-      </c>
-      <c r="O19" t="s">
-        <v>208</v>
-      </c>
-      <c r="P19" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>213</v>
-      </c>
-      <c r="R19">
-        <v>619288243159</v>
-      </c>
-      <c r="U19" t="s">
-        <v>221</v>
-      </c>
-      <c r="V19" t="s">
-        <v>239</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>246</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD19">
-        <v>24</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>270</v>
-      </c>
-      <c r="BF19">
-        <v>1594</v>
-      </c>
-      <c r="BG19" t="s">
-        <v>282</v>
-      </c>
-      <c r="BH19">
-        <v>1</v>
-      </c>
-      <c r="BI19" t="s">
-        <v>286</v>
-      </c>
-      <c r="BJ19" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL19" t="s">
-        <v>174</v>
-      </c>
-      <c r="BM19" t="s">
-        <v>312</v>
-      </c>
-      <c r="BN19" t="s">
-        <v>322</v>
-      </c>
-      <c r="BO19" t="s">
-        <v>335</v>
-      </c>
-      <c r="BP19" t="s">
-        <v>324</v>
-      </c>
-      <c r="BQ19">
-        <v>1</v>
-      </c>
-      <c r="BR19">
-        <v>3</v>
-      </c>
-      <c r="BS19" t="s">
-        <v>350</v>
-      </c>
-      <c r="BT19">
-        <v>2190</v>
-      </c>
-      <c r="BU19" t="s">
-        <v>360</v>
-      </c>
-      <c r="BV19" t="s">
-        <v>367</v>
-      </c>
-      <c r="BW19">
-        <v>90300</v>
-      </c>
-      <c r="BX19" t="s">
-        <v>376</v>
-      </c>
-      <c r="BY19" t="s">
-        <v>378</v>
-      </c>
-      <c r="BZ19">
-        <v>2026</v>
-      </c>
-      <c r="CA19">
-        <v>50</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>391</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>408</v>
-      </c>
-      <c r="CD19" t="s">
-        <v>423</v>
-      </c>
-      <c r="CE19" t="s">
-        <v>426</v>
-      </c>
-      <c r="DE19" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="20" spans="1:109">
-      <c r="A20">
-        <v>1249239</v>
-      </c>
-      <c r="B20" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" t="s">
-        <v>175</v>
-      </c>
-      <c r="F20">
-        <v>543813007337</v>
-      </c>
-      <c r="G20" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" t="s">
-        <v>182</v>
-      </c>
-      <c r="I20">
-        <v>231</v>
-      </c>
-      <c r="J20" t="s">
-        <v>198</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>201</v>
-      </c>
-      <c r="M20">
-        <v>130</v>
-      </c>
-      <c r="N20" t="s">
-        <v>205</v>
-      </c>
-      <c r="O20" t="s">
-        <v>207</v>
-      </c>
-      <c r="P20" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>214</v>
-      </c>
-      <c r="R20">
-        <v>1.2021509703101E+17</v>
-      </c>
-      <c r="S20" t="s">
-        <v>215</v>
-      </c>
-      <c r="U20" t="s">
-        <v>219</v>
-      </c>
-      <c r="V20" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>3</v>
-      </c>
-      <c r="BC20" t="s">
-        <v>265</v>
-      </c>
-      <c r="BD20">
-        <v>9</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>267</v>
-      </c>
-      <c r="BF20">
-        <v>1512</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>283</v>
-      </c>
-      <c r="BH20">
-        <v>7</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>285</v>
-      </c>
-      <c r="BJ20" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL20" t="s">
-        <v>175</v>
-      </c>
-      <c r="BM20" t="s">
-        <v>313</v>
-      </c>
-      <c r="BN20" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO20" t="s">
-        <v>324</v>
-      </c>
-      <c r="BP20" t="s">
-        <v>346</v>
-      </c>
-      <c r="BQ20">
-        <v>11</v>
-      </c>
-      <c r="BR20">
-        <v>101</v>
-      </c>
-      <c r="BS20" t="s">
-        <v>349</v>
-      </c>
-      <c r="BT20">
-        <v>2251</v>
-      </c>
-      <c r="BU20" t="s">
-        <v>361</v>
-      </c>
-      <c r="BV20" t="s">
-        <v>365</v>
-      </c>
-      <c r="BW20">
-        <v>60000</v>
-      </c>
-      <c r="BX20" t="s">
-        <v>376</v>
-      </c>
-      <c r="BY20" t="s">
-        <v>378</v>
-      </c>
-      <c r="BZ20">
-        <v>2026</v>
-      </c>
-      <c r="CA20">
-        <v>50</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>392</v>
-      </c>
-      <c r="CC20" t="s">
-        <v>409</v>
-      </c>
-      <c r="CD20" t="s">
-        <v>165</v>
-      </c>
-      <c r="CE20" t="s">
-        <v>426</v>
-      </c>
-      <c r="DE20" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="21" spans="1:109">
-      <c r="A21">
-        <v>1612631</v>
-      </c>
-      <c r="B21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" t="s">
-        <v>176</v>
-      </c>
-      <c r="F21">
-        <v>5493876116543</v>
-      </c>
-      <c r="G21" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" t="s">
-        <v>181</v>
-      </c>
-      <c r="I21">
-        <v>11</v>
-      </c>
-      <c r="J21" t="s">
-        <v>185</v>
-      </c>
-      <c r="K21">
-        <v>3</v>
-      </c>
-      <c r="L21" t="s">
-        <v>200</v>
-      </c>
-      <c r="M21">
-        <v>41</v>
-      </c>
-      <c r="S21" t="s">
-        <v>215</v>
-      </c>
-      <c r="U21" t="s">
-        <v>218</v>
-      </c>
-      <c r="V21" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>257</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1</v>
-      </c>
-      <c r="BC21" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD21">
-        <v>24</v>
-      </c>
-      <c r="BE21" t="s">
-        <v>270</v>
-      </c>
-      <c r="BF21">
-        <v>1050</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>276</v>
-      </c>
-      <c r="BH21">
-        <v>1</v>
-      </c>
-      <c r="BI21" t="s">
-        <v>286</v>
-      </c>
-      <c r="BJ21" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK21" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL21" t="s">
-        <v>176</v>
-      </c>
-      <c r="BM21" t="s">
-        <v>314</v>
-      </c>
-      <c r="BN21" t="s">
-        <v>323</v>
-      </c>
-      <c r="BO21" t="s">
-        <v>336</v>
-      </c>
-      <c r="BP21" t="s">
-        <v>347</v>
-      </c>
-      <c r="BQ21">
-        <v>1</v>
-      </c>
-      <c r="BR21">
-        <v>3</v>
-      </c>
-      <c r="BS21" t="s">
-        <v>350</v>
-      </c>
-      <c r="BT21">
-        <v>10</v>
-      </c>
-      <c r="BU21" t="s">
-        <v>359</v>
-      </c>
-      <c r="BV21" t="s">
-        <v>373</v>
-      </c>
-      <c r="BW21">
-        <v>56500</v>
-      </c>
-      <c r="BX21" t="s">
-        <v>376</v>
-      </c>
-      <c r="BY21" t="s">
-        <v>378</v>
-      </c>
-      <c r="BZ21">
-        <v>2026</v>
-      </c>
-      <c r="CC21" t="s">
-        <v>410</v>
-      </c>
-      <c r="CD21" t="s">
-        <v>424</v>
-      </c>
-      <c r="CE21" t="s">
-        <v>426</v>
-      </c>
-      <c r="DE21" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="22" spans="1:109">
-      <c r="A22">
-        <v>1727395</v>
-      </c>
-      <c r="B22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" t="s">
-        <v>146</v>
-      </c>
-      <c r="D22" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" t="s">
-        <v>177</v>
-      </c>
-      <c r="F22">
-        <v>5493874489311</v>
-      </c>
-      <c r="G22" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" t="s">
-        <v>182</v>
-      </c>
-      <c r="I22">
-        <v>123</v>
-      </c>
-      <c r="J22" t="s">
-        <v>199</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22" t="s">
-        <v>201</v>
-      </c>
-      <c r="M22">
-        <v>3</v>
-      </c>
-      <c r="S22" t="s">
-        <v>215</v>
-      </c>
-      <c r="T22" t="s">
-        <v>216</v>
-      </c>
-      <c r="U22" t="s">
-        <v>219</v>
-      </c>
-      <c r="V22" t="s">
-        <v>242</v>
-      </c>
-      <c r="W22" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>246</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>167</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>258</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1</v>
-      </c>
-      <c r="BC22" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD22">
-        <v>9</v>
-      </c>
-      <c r="BE22" t="s">
-        <v>267</v>
-      </c>
-      <c r="BF22">
-        <v>1644</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>284</v>
-      </c>
-      <c r="BH22">
-        <v>1</v>
-      </c>
-      <c r="BI22" t="s">
-        <v>286</v>
-      </c>
-      <c r="BJ22" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK22" t="s">
-        <v>288</v>
-      </c>
-      <c r="BL22" t="s">
-        <v>177</v>
-      </c>
-      <c r="BM22" t="s">
-        <v>315</v>
-      </c>
-      <c r="BN22" t="s">
-        <v>146</v>
-      </c>
-      <c r="BO22" t="s">
-        <v>337</v>
-      </c>
-      <c r="BP22" t="s">
-        <v>348</v>
-      </c>
-      <c r="BQ22">
-        <v>1</v>
-      </c>
-      <c r="BR22">
-        <v>2</v>
-      </c>
-      <c r="BS22" t="s">
-        <v>351</v>
-      </c>
-      <c r="BT22">
-        <v>2491</v>
-      </c>
-      <c r="BU22" t="s">
-        <v>362</v>
-      </c>
-      <c r="BV22" t="s">
-        <v>374</v>
-      </c>
-      <c r="BW22">
-        <v>175000</v>
-      </c>
-      <c r="BX22" t="s">
-        <v>376</v>
-      </c>
-      <c r="BY22" t="s">
-        <v>378</v>
-      </c>
-      <c r="BZ22">
-        <v>2026</v>
-      </c>
-      <c r="CA22">
-        <v>50</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>393</v>
-      </c>
-      <c r="CC22" t="s">
-        <v>411</v>
-      </c>
-      <c r="CD22" t="s">
-        <v>425</v>
-      </c>
-      <c r="CE22" t="s">
-        <v>426</v>
-      </c>
-      <c r="DE22" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
